--- a/InputData/endo-learn/BGBSC/BAU Global Battery Storage Cap.xlsx
+++ b/InputData/endo-learn/BGBSC/BAU Global Battery Storage Cap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\endo-learn\BGBSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\eps-us\InputData\endo-learn\BGBSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D86885A-E992-4AA7-BBEC-5E9606EA0A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CA9D85-524A-4A75-AE82-BEE5D1E41131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="495" yWindow="240" windowWidth="18480" windowHeight="17100" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -2838,17 +2838,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="60.81640625" customWidth="1"/>
+    <col min="2" max="2" width="60.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2856,62 +2856,62 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="9">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="9">
         <v>2024</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
     </row>
   </sheetData>
@@ -2923,12 +2923,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AF5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.1796875" customWidth="1"/>
+    <col min="1" max="1" width="35.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>21</v>
       </c>
@@ -2936,10 +2936,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>2020</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>3018.3651290394619</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -3269,26 +3269,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AF16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.7265625" customWidth="1"/>
-    <col min="3" max="3" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3296,7 +3296,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>2020</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -3345,12 +3345,12 @@
         <v>3630152910.6631694</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:32" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>3630.1529106631624</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -3602,7 +3602,7 @@
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>81549620.895449489</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="14">
@@ -3775,7 +3775,7 @@
       <c r="AE15" s="12"/>
       <c r="AF15" s="12"/>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B16" s="8">
         <f t="shared" ref="B16:AF16" si="1" xml:space="preserve"> (83.94318 + (-3.575905 - 83.94318)/(1 + (B11/2030.462)^372.9304))*1000000</f>
         <v>7551143.5426923158</v>
@@ -3911,31 +3911,31 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AG15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="67.453125" customWidth="1"/>
-    <col min="2" max="3" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="67.42578125" customWidth="1"/>
+    <col min="2" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="32" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2020</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -4159,17 +4159,17 @@
         <v>12073460.516157847</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>2020</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="AG12" s="16"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>84210167.376524493</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AF15" s="16"/>
     </row>
   </sheetData>
@@ -4539,25 +4539,25 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" customWidth="1"/>
-    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="8">
-        <f>Summary!E6+Summary!E13</f>
-        <v>1952167.6732656616</v>
+        <f>BGBSC!B2</f>
+        <v>2989340.257733738</v>
       </c>
     </row>
   </sheetData>
@@ -4571,14 +4571,14 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" customWidth="1"/>
-    <col min="2" max="8" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="30" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="30" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>2024</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
